--- a/data/processed/harmonization/Nitrogen__Total_nitrogen/10.15485_1785525/10.15485_1785525_soil_Nitrogen__Total_nitrogen.xlsx
+++ b/data/processed/harmonization/Nitrogen__Total_nitrogen/10.15485_1785525/10.15485_1785525_soil_Nitrogen__Total_nitrogen.xlsx
@@ -431,8 +431,8 @@
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="54" customWidth="1" min="2" max="2"/>
-    <col width="4" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
     <col width="26" customWidth="1" min="7" max="7"/>
@@ -518,12 +518,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2:2</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -614,12 +614,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3:3</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
@@ -662,12 +662,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4:4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
@@ -710,12 +710,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5:5</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -758,12 +758,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1:6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -806,12 +806,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2:7</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
@@ -854,12 +854,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3:8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
@@ -902,12 +902,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4:9</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -950,12 +950,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5:10</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
@@ -998,12 +998,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6:11</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8:12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>22:15</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
